--- a/sources/armorking_step3.xlsx
+++ b/sources/armorking_step3.xlsx
@@ -1004,6 +1004,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
@@ -1036,6 +1041,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>da3a1275-cb0c-4106-8641-cfa9ccdf3ec7</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>da3a1275-cb0c-4106-8641-cfa9ccdf3ec7</t>
@@ -1073,6 +1083,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>c59ded73-4975-409c-9fcb-97f64f823e1f</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>c59ded73-4975-409c-9fcb-97f64f823e1f</t>
@@ -1110,6 +1125,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4bfbb956-22f3-4aa3-8b36-b331246b3633</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>4bfbb956-22f3-4aa3-8b36-b331246b3633</t>
@@ -1147,6 +1167,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>b017afe8-35fe-4676-b2eb-d81bccc55df5</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>b017afe8-35fe-4676-b2eb-d81bccc55df5</t>
@@ -1189,6 +1214,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4032df9b-cac0-4300-a750-9f6328f0125c</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>4032df9b-cac0-4300-a750-9f6328f0125c</t>
@@ -1226,6 +1256,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>03ae734c-c034-4a04-8b1f-1969120d9045</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>03ae734c-c034-4a04-8b1f-1969120d9045</t>
@@ -1261,6 +1296,11 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>f38eafdb-7ad2-4d22-a656-ee63cb402a1e</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -4921,6 +4961,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
+        </is>
+      </c>
       <c r="O96" t="inlineStr">
         <is>
           <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
@@ -4953,6 +4998,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ab4325ea-0934-4517-856d-7640da4c01f7</t>
+        </is>
+      </c>
       <c r="O97" t="inlineStr">
         <is>
           <t>ab4325ea-0934-4517-856d-7640da4c01f7</t>
@@ -4990,6 +5040,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
+        </is>
+      </c>
       <c r="O98" t="inlineStr">
         <is>
           <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
@@ -5027,6 +5082,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>fc691ddf-15db-4695-a8e9-7430fe664066</t>
+        </is>
+      </c>
       <c r="O99" t="inlineStr">
         <is>
           <t>fc691ddf-15db-4695-a8e9-7430fe664066</t>
@@ -5062,6 +5122,11 @@
       <c r="K100" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>fdcf2a53-d956-49ec-97b6-76739cea2462</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -5191,6 +5256,11 @@
           <t>hhmmhLLLmm</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>21571b37-4525-4b34-9433-0797a86f473f</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
           <t>21571b37-4525-4b34-9433-0797a86f473f</t>
@@ -5216,6 +5286,11 @@
       <c r="I105" t="inlineStr">
         <is>
           <t>hmmhLLLmm</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>3d0c8edd-a764-4366-833c-c7fe06fc9cc8</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
